--- a/Checklist - Artefato 5.xlsx
+++ b/Checklist - Artefato 5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucpredu-my.sharepoint.com/personal/ferrarini_isabela_pucpr_edu_br/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Fernandes\Downloads\ChecklistQualidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B4DFB20-DD77-44A8-8DC1-ED06A84EBDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09F38D0-49D5-4C10-9249-688259076355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>N°</t>
   </si>
@@ -137,13 +137,28 @@
   </si>
   <si>
     <t>Tempo total:</t>
+  </si>
+  <si>
+    <t>Aderência Por Área</t>
+  </si>
+  <si>
+    <t>Total de Perguntas</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Não Aplicavél</t>
+  </si>
+  <si>
+    <t>Aderência</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -184,8 +199,30 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,6 +233,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFA6124E"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6124E"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -278,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -288,14 +331,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -571,7 +630,7 @@
     <col min="6" max="6" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="46.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +674,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -629,7 +688,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -643,7 +702,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -657,7 +716,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -671,7 +730,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -685,7 +744,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -699,7 +758,7 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -713,7 +772,7 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -727,7 +786,7 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -741,7 +800,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -755,7 +814,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -769,7 +828,7 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -783,7 +842,7 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -797,7 +856,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -811,7 +870,7 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -825,7 +884,7 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -839,7 +898,7 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -853,7 +912,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -867,7 +926,7 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -881,7 +940,7 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -896,60 +955,101 @@
       <c r="H21" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="6"/>
+      <c r="C23" s="5"/>
+      <c r="E23" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>30</v>
       </c>
+      <c r="E24" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>32</v>
       </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="12"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>34</v>
       </c>
+      <c r="E26" s="13">
+        <v>0</v>
+      </c>
+      <c r="F26" s="13">
+        <v>0</v>
+      </c>
+      <c r="G26" s="13">
+        <v>0</v>
+      </c>
+      <c r="H26" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="7"/>
-      <c r="C27" s="8"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="8"/>
+      <c r="C29" s="7"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="8"/>
+      <c r="C30" s="7"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -958,6 +1058,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CCF20922A0DE34DA3357EDA40AE3850" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df2c289d3a08b18055ba2ef47a57998b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="aed73f09-bf5d-4147-a3d9-eca4840d3416" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91dac5f1c2bd6141b57005fd2a16424c" ns3:_="">
     <xsd:import namespace="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
@@ -1107,24 +1224,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E08FA29-7FA5-4A5A-8E28-BAB0E9A4DCE2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E117C1D-E420-4FD7-BF6E-ADA619128D90}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C95CE609-CCD5-4881-A2BF-E18B42C59927}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1140,28 +1264,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E117C1D-E420-4FD7-BF6E-ADA619128D90}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E08FA29-7FA5-4A5A-8E28-BAB0E9A4DCE2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>